--- a/src/fixtures/sample/gstr2b-2025-12.xlsx
+++ b/src/fixtures/sample/gstr2b-2025-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2025/033</v>
+        <v>S01/2025/023</v>
       </c>
       <c r="D6" t="str">
-        <v>15/12/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="E6">
-        <v>558140</v>
+        <v>555780</v>
       </c>
       <c r="F6">
-        <v>473000</v>
+        <v>471000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>42570</v>
+        <v>42390</v>
       </c>
       <c r="I6">
-        <v>42570</v>
+        <v>42390</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2026-01</v>
       </c>
       <c r="L6" t="str">
-        <v>11/01/2026</v>
+        <v>16/01/2026</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>29AAKFK3390B1ZB</v>
+        <v>27AAPFM4821K1ZV</v>
       </c>
       <c r="B7" t="str">
-        <v>Kaveri Packaging</v>
+        <v>Mahesh Steel Traders</v>
       </c>
       <c r="C7" t="str">
-        <v>S03/2025/011</v>
+        <v>S01/2025/032</v>
       </c>
       <c r="D7" t="str">
-        <v>22/10/2025</v>
+        <v>18/12/2025</v>
       </c>
       <c r="E7">
-        <v>146320</v>
+        <v>566400</v>
       </c>
       <c r="F7">
-        <v>124000</v>
+        <v>480000</v>
       </c>
       <c r="G7">
-        <v>22320</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2026-01</v>
       </c>
       <c r="L7" t="str">
-        <v>18/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,19 +564,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C8" t="str">
-        <v>S03/2025/012</v>
+        <v>S03/2025/011</v>
       </c>
       <c r="D8" t="str">
-        <v>23/10/2025</v>
+        <v>02/10/2025</v>
       </c>
       <c r="E8">
-        <v>146320</v>
+        <v>126260</v>
       </c>
       <c r="F8">
-        <v>124000</v>
+        <v>107000</v>
       </c>
       <c r="G8">
-        <v>22320</v>
+        <v>19260</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2026-01</v>
       </c>
       <c r="L8" t="str">
-        <v>18/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -611,19 +611,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C9" t="str">
-        <v>S03/2025/021</v>
+        <v>S03/2025/012</v>
       </c>
       <c r="D9" t="str">
-        <v>09/11/2025</v>
+        <v>15/10/2025</v>
       </c>
       <c r="E9">
-        <v>141600</v>
+        <v>134520</v>
       </c>
       <c r="F9">
-        <v>120000</v>
+        <v>114000</v>
       </c>
       <c r="G9">
-        <v>21600</v>
+        <v>20520</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2026-01</v>
       </c>
       <c r="L9" t="str">
-        <v>15/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -658,19 +658,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C10" t="str">
-        <v>S03/2025/022</v>
+        <v>S03/2025/021</v>
       </c>
       <c r="D10" t="str">
-        <v>19/11/2025</v>
+        <v>17/11/2025</v>
       </c>
       <c r="E10">
-        <v>128620</v>
+        <v>145140</v>
       </c>
       <c r="F10">
-        <v>109000</v>
+        <v>123000</v>
       </c>
       <c r="G10">
-        <v>19620</v>
+        <v>22140</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2026-01</v>
       </c>
       <c r="L10" t="str">
-        <v>16/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -705,19 +705,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C11" t="str">
-        <v>S03/2025/031</v>
+        <v>S03/2025/022</v>
       </c>
       <c r="D11" t="str">
-        <v>03/12/2025</v>
+        <v>04/11/2025</v>
       </c>
       <c r="E11">
-        <v>125080</v>
+        <v>133340</v>
       </c>
       <c r="F11">
-        <v>106000</v>
+        <v>113000</v>
       </c>
       <c r="G11">
-        <v>19080</v>
+        <v>20340</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2026-01</v>
       </c>
       <c r="L11" t="str">
-        <v>18/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -752,19 +752,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C12" t="str">
-        <v>S03/2025/032</v>
+        <v>S03/2025/031</v>
       </c>
       <c r="D12" t="str">
-        <v>02/12/2025</v>
+        <v>04/12/2025</v>
       </c>
       <c r="E12">
-        <v>126260</v>
+        <v>149860</v>
       </c>
       <c r="F12">
-        <v>107000</v>
+        <v>127000</v>
       </c>
       <c r="G12">
-        <v>19260</v>
+        <v>22860</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -793,25 +793,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>29AAKFK3390B1ZB</v>
       </c>
       <c r="B13" t="str">
-        <v>Anand Polymers</v>
+        <v>Kaveri Packaging</v>
       </c>
       <c r="C13" t="str">
-        <v>S05/2025/031</v>
+        <v>S03/2025/032</v>
       </c>
       <c r="D13" t="str">
-        <v>11/12/2025</v>
+        <v>24/12/2025</v>
       </c>
       <c r="E13">
-        <v>370520</v>
+        <v>147500</v>
       </c>
       <c r="F13">
-        <v>314000</v>
+        <v>125000</v>
       </c>
       <c r="G13">
-        <v>56520</v>
+        <v>22500</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -846,19 +846,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C14" t="str">
-        <v>S05/2025/032</v>
+        <v>S05/2025/031</v>
       </c>
       <c r="D14" t="str">
-        <v>22/12/2025</v>
+        <v>15/12/2025</v>
       </c>
       <c r="E14">
-        <v>377600</v>
+        <v>357540</v>
       </c>
       <c r="F14">
-        <v>320000</v>
+        <v>303000</v>
       </c>
       <c r="G14">
-        <v>57600</v>
+        <v>54540</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2026-01</v>
       </c>
       <c r="L14" t="str">
-        <v>14/01/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -893,19 +893,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C15" t="str">
-        <v>S05/2025/033</v>
+        <v>S05/2025/032</v>
       </c>
       <c r="D15" t="str">
         <v>14/12/2025</v>
       </c>
       <c r="E15">
-        <v>372880</v>
+        <v>368160</v>
       </c>
       <c r="F15">
-        <v>316000</v>
+        <v>312000</v>
       </c>
       <c r="G15">
-        <v>56880</v>
+        <v>56160</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>2026-01</v>
       </c>
       <c r="L15" t="str">
-        <v>12/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
@@ -934,31 +934,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B16" t="str">
-        <v>Surya Electricals</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C16" t="str">
-        <v>SE 31</v>
+        <v>S05/2025/033</v>
       </c>
       <c r="D16" t="str">
-        <v>12/12/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="E16">
-        <v>172280</v>
+        <v>357540</v>
       </c>
       <c r="F16">
-        <v>146000</v>
+        <v>303000</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>54540</v>
       </c>
       <c r="H16">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2026-01</v>
       </c>
       <c r="L16" t="str">
-        <v>13/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -990,22 +990,22 @@
         <v>SE 31</v>
       </c>
       <c r="D17" t="str">
-        <v>04/12/2025</v>
+        <v>19/12/2025</v>
       </c>
       <c r="E17">
-        <v>162840</v>
+        <v>154580</v>
       </c>
       <c r="F17">
-        <v>138000</v>
+        <v>131000</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>12420</v>
+        <v>11790</v>
       </c>
       <c r="I17">
-        <v>12420</v>
+        <v>11790</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>2026-01</v>
       </c>
       <c r="L17" t="str">
-        <v>08/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
@@ -1028,31 +1028,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B18" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C18" t="str">
-        <v>S07/2025/031</v>
+        <v>SE 31</v>
       </c>
       <c r="D18" t="str">
-        <v>11/12/2025</v>
+        <v>26/12/2025</v>
       </c>
       <c r="E18">
-        <v>247800</v>
+        <v>174640</v>
       </c>
       <c r="F18">
-        <v>210000</v>
+        <v>148000</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>18900</v>
+        <v>13320</v>
       </c>
       <c r="I18">
-        <v>18900</v>
+        <v>13320</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>2026-01</v>
       </c>
       <c r="L18" t="str">
-        <v>08/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="M18" t="str">
         <v>Yes</v>
@@ -1081,25 +1081,25 @@
         <v>Nilkanth Traders</v>
       </c>
       <c r="C19" t="str">
-        <v>S07/2025/032</v>
+        <v>S07/2025/031</v>
       </c>
       <c r="D19" t="str">
-        <v>05/12/2025</v>
+        <v>19/12/2025</v>
       </c>
       <c r="E19">
-        <v>256060</v>
+        <v>239540</v>
       </c>
       <c r="F19">
-        <v>217000</v>
+        <v>203000</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>19530</v>
+        <v>18270</v>
       </c>
       <c r="I19">
-        <v>19530</v>
+        <v>18270</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2026-01</v>
       </c>
       <c r="L19" t="str">
-        <v>14/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1122,31 +1122,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B20" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C20" t="str">
-        <v>S08/2025/031</v>
+        <v>S07/2025/032</v>
       </c>
       <c r="D20" t="str">
         <v>13/12/2025</v>
       </c>
       <c r="E20">
-        <v>211220</v>
+        <v>243080</v>
       </c>
       <c r="F20">
-        <v>179000</v>
+        <v>206000</v>
       </c>
       <c r="G20">
-        <v>32220</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>18540</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>18540</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1175,19 +1175,19 @@
         <v>Ratna Chemicals</v>
       </c>
       <c r="C21" t="str">
-        <v>S08/2025/032</v>
+        <v>S08/2025/031</v>
       </c>
       <c r="D21" t="str">
-        <v>08/12/2025</v>
+        <v>24/12/2025</v>
       </c>
       <c r="E21">
-        <v>201780</v>
+        <v>220660</v>
       </c>
       <c r="F21">
-        <v>171000</v>
+        <v>187000</v>
       </c>
       <c r="G21">
-        <v>30780</v>
+        <v>33660</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2026-01</v>
       </c>
       <c r="L21" t="str">
-        <v>14/01/2026</v>
+        <v>13/01/2026</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1216,31 +1216,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B22" t="str">
-        <v>Metro Motors</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C22" t="str">
-        <v>S09/2025/031</v>
+        <v>S08/2025/032</v>
       </c>
       <c r="D22" t="str">
-        <v>16/12/2025</v>
+        <v>23/12/2025</v>
       </c>
       <c r="E22">
-        <v>1041940</v>
+        <v>198240</v>
       </c>
       <c r="F22">
-        <v>883000</v>
+        <v>168000</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>30240</v>
       </c>
       <c r="H22">
-        <v>79470</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>79470</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>08/01/2026</v>
       </c>
       <c r="M22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N22" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O22" t="str">
         <v>N</v>
@@ -1263,31 +1263,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B23" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C23" t="str">
-        <v>S10/2025/031</v>
+        <v>S09/2025/031</v>
       </c>
       <c r="D23" t="str">
-        <v>10/12/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="E23">
-        <v>309160</v>
+        <v>1047840</v>
       </c>
       <c r="F23">
-        <v>262000</v>
+        <v>888000</v>
       </c>
       <c r="G23">
-        <v>47160</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>79920</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>79920</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>14/01/2026</v>
       </c>
       <c r="M23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O23" t="str">
         <v>N</v>
@@ -1316,19 +1316,19 @@
         <v>Vindhya Alloys</v>
       </c>
       <c r="C24" t="str">
-        <v>S10/2025/032</v>
+        <v>S10/2025/031</v>
       </c>
       <c r="D24" t="str">
-        <v>17/12/2025</v>
+        <v>03/12/2025</v>
       </c>
       <c r="E24">
-        <v>322140</v>
+        <v>298540</v>
       </c>
       <c r="F24">
-        <v>273000</v>
+        <v>253000</v>
       </c>
       <c r="G24">
-        <v>49140</v>
+        <v>45540</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2026-01</v>
       </c>
       <c r="L24" t="str">
-        <v>11/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1357,31 +1357,31 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B25" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C25" t="str">
-        <v>S12/2025/031</v>
+        <v>S10/2025/032</v>
       </c>
       <c r="D25" t="str">
-        <v>10/12/2025</v>
+        <v>25/12/2025</v>
       </c>
       <c r="E25">
-        <v>198240</v>
+        <v>305620</v>
       </c>
       <c r="F25">
-        <v>168000</v>
+        <v>259000</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>46620</v>
       </c>
       <c r="H25">
-        <v>15120</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>15120</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2026-01</v>
       </c>
       <c r="L25" t="str">
-        <v>11/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1410,25 +1410,25 @@
         <v>Bharat Office Supplies</v>
       </c>
       <c r="C26" t="str">
-        <v>S12/2025/032</v>
+        <v>S12/2025/021</v>
       </c>
       <c r="D26" t="str">
-        <v>10/12/2025</v>
+        <v>04/11/2025</v>
       </c>
       <c r="E26">
-        <v>204140</v>
+        <v>185260</v>
       </c>
       <c r="F26">
-        <v>173000</v>
+        <v>157000</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>15570</v>
+        <v>14130</v>
       </c>
       <c r="I26">
-        <v>15570</v>
+        <v>14130</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2026-01</v>
       </c>
       <c r="L26" t="str">
-        <v>13/01/2026</v>
+        <v>10/01/2026</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1451,31 +1451,31 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>27AAGFK5561R1ZL</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B27" t="str">
-        <v>Konkan Hardware</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C27" t="str">
-        <v>S13/2025/031</v>
+        <v>S12/2025/031</v>
       </c>
       <c r="D27" t="str">
-        <v>09/12/2025</v>
+        <v>04/12/2025</v>
       </c>
       <c r="E27">
-        <v>73160</v>
+        <v>178180</v>
       </c>
       <c r="F27">
-        <v>62000</v>
+        <v>151000</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>5580</v>
+        <v>13590</v>
       </c>
       <c r="I27">
-        <v>5580</v>
+        <v>13590</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>2026-01</v>
       </c>
       <c r="L27" t="str">
-        <v>10/01/2026</v>
+        <v>16/01/2026</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1498,31 +1498,31 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>24AAACT3398E1ZE</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B28" t="str">
-        <v>Trident Paper Mills</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C28" t="str">
-        <v>S14/2025/031</v>
+        <v>S12/2025/032</v>
       </c>
       <c r="D28" t="str">
-        <v>19/12/2025</v>
+        <v>04/12/2025</v>
       </c>
       <c r="E28">
-        <v>152220</v>
+        <v>177000</v>
       </c>
       <c r="F28">
-        <v>129000</v>
+        <v>150000</v>
       </c>
       <c r="G28">
-        <v>23220</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2026-01</v>
       </c>
       <c r="L28" t="str">
-        <v>09/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1545,31 +1545,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>27AAGFK5561R1ZL</v>
       </c>
       <c r="B29" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Konkan Hardware</v>
       </c>
       <c r="C29" t="str">
-        <v>S15/2025/032</v>
+        <v>S13/2025/031</v>
       </c>
       <c r="D29" t="str">
-        <v>18/12/2025</v>
+        <v>24/12/2025</v>
       </c>
       <c r="E29">
-        <v>49560</v>
+        <v>74340</v>
       </c>
       <c r="F29">
-        <v>42000</v>
+        <v>63000</v>
       </c>
       <c r="G29">
-        <v>7560</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>5670</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>5670</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2026-01</v>
       </c>
       <c r="L29" t="str">
-        <v>12/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1592,25 +1592,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>24AAACT3398E1ZE</v>
       </c>
       <c r="B30" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Trident Paper Mills</v>
       </c>
       <c r="C30" t="str">
-        <v>S15/2025/033</v>
+        <v>S14/2025/031</v>
       </c>
       <c r="D30" t="str">
-        <v>15/12/2025</v>
+        <v>05/12/2025</v>
       </c>
       <c r="E30">
-        <v>40120</v>
+        <v>153400</v>
       </c>
       <c r="F30">
-        <v>34000</v>
+        <v>130000</v>
       </c>
       <c r="G30">
-        <v>6120</v>
+        <v>23400</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2026-01</v>
       </c>
       <c r="L30" t="str">
-        <v>08/01/2026</v>
+        <v>13/01/2026</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B31" t="str">
-        <v>Orion Software Services</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C31" t="str">
-        <v>S16/2025/031</v>
+        <v>S15/2025/031</v>
       </c>
       <c r="D31" t="str">
-        <v>07/12/2025</v>
+        <v>26/12/2025</v>
       </c>
       <c r="E31">
-        <v>83780</v>
+        <v>59000</v>
       </c>
       <c r="F31">
-        <v>71000</v>
+        <v>50000</v>
       </c>
       <c r="G31">
-        <v>12780</v>
+        <v>9000</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1686,25 +1686,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09AAHFG4423Y1ZH</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B32" t="str">
-        <v>Ganga Textiles</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C32" t="str">
-        <v>S17/2025/031</v>
+        <v>S15/2025/032</v>
       </c>
       <c r="D32" t="str">
-        <v>12/12/2025</v>
+        <v>03/12/2025</v>
       </c>
       <c r="E32">
-        <v>44840</v>
+        <v>56640</v>
       </c>
       <c r="F32">
-        <v>38000</v>
+        <v>48000</v>
       </c>
       <c r="G32">
-        <v>6840</v>
+        <v>8640</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1733,31 +1733,31 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B33" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C33" t="str">
-        <v>S18/2025/022</v>
+        <v>S15/2025/033</v>
       </c>
       <c r="D33" t="str">
-        <v>24/11/2025</v>
+        <v>03/12/2025</v>
       </c>
       <c r="E33">
-        <v>155760</v>
+        <v>38940</v>
       </c>
       <c r="F33">
-        <v>132000</v>
+        <v>33000</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>5940</v>
       </c>
       <c r="H33">
-        <v>11880</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>11880</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>2026-01</v>
       </c>
       <c r="L33" t="str">
-        <v>12/01/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
@@ -1780,31 +1780,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B34" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C34" t="str">
-        <v>S18/2025/031</v>
+        <v>S16/2025/031</v>
       </c>
       <c r="D34" t="str">
-        <v>03/12/2025</v>
+        <v>17/12/2025</v>
       </c>
       <c r="E34">
-        <v>159300</v>
+        <v>60180</v>
       </c>
       <c r="F34">
-        <v>135000</v>
+        <v>51000</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>9180</v>
       </c>
       <c r="H34">
-        <v>12150</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>12150</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2026-01</v>
       </c>
       <c r="L34" t="str">
-        <v>11/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B35" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C35" t="str">
-        <v>S18/2025/032</v>
+        <v>S16/2025/032</v>
       </c>
       <c r="D35" t="str">
-        <v>24/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="E35">
-        <v>146320</v>
+        <v>66080</v>
       </c>
       <c r="F35">
-        <v>124000</v>
+        <v>56000</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>10080</v>
       </c>
       <c r="H35">
-        <v>11160</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>11160</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2026-01</v>
       </c>
       <c r="L35" t="str">
-        <v>15/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1874,31 +1874,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>09AAHFG4423Y1ZH</v>
       </c>
       <c r="B36" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Ganga Textiles</v>
       </c>
       <c r="C36" t="str">
-        <v>S18/2025/033</v>
+        <v>S17/2025/031</v>
       </c>
       <c r="D36" t="str">
-        <v>23/12/2025</v>
+        <v>03/12/2025</v>
       </c>
       <c r="E36">
-        <v>160480</v>
+        <v>47200</v>
       </c>
       <c r="F36">
-        <v>136000</v>
+        <v>40000</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="H36">
-        <v>12240</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>12240</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2026-01</v>
       </c>
       <c r="L36" t="str">
-        <v>12/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1921,31 +1921,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B37" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C37" t="str">
-        <v>S19/2025/032</v>
+        <v>S18/2025/031</v>
       </c>
       <c r="D37" t="str">
-        <v>25/12/2025</v>
+        <v>13/12/2025</v>
       </c>
       <c r="E37">
-        <v>108560</v>
+        <v>167560</v>
       </c>
       <c r="F37">
-        <v>92000</v>
+        <v>142000</v>
       </c>
       <c r="G37">
-        <v>16560</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>12780</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>12780</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2026-01</v>
       </c>
       <c r="L37" t="str">
-        <v>09/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1968,31 +1968,31 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B38" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C38" t="str">
-        <v>S20/2025/031</v>
+        <v>S18/2025/032</v>
       </c>
       <c r="D38" t="str">
-        <v>08/12/2025</v>
+        <v>13/12/2025</v>
       </c>
       <c r="E38">
-        <v>151040</v>
+        <v>164020</v>
       </c>
       <c r="F38">
-        <v>128000</v>
+        <v>139000</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>11520</v>
+        <v>12510</v>
       </c>
       <c r="I38">
-        <v>11520</v>
+        <v>12510</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2026-01</v>
       </c>
       <c r="L38" t="str">
-        <v>15/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2015,31 +2015,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B39" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C39" t="str">
-        <v>S20/2025/032</v>
+        <v>S18/2025/033</v>
       </c>
       <c r="D39" t="str">
-        <v>05/12/2025</v>
+        <v>17/12/2025</v>
       </c>
       <c r="E39">
-        <v>134520</v>
+        <v>148680</v>
       </c>
       <c r="F39">
-        <v>114000</v>
+        <v>126000</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>10260</v>
+        <v>11340</v>
       </c>
       <c r="I39">
-        <v>10260</v>
+        <v>11340</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2026-01</v>
       </c>
       <c r="L39" t="str">
-        <v>10/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2062,25 +2062,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B40" t="str">
-        <v>Nova Instruments</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C40" t="str">
-        <v>S21/2025/031</v>
+        <v>S19/2025/022</v>
       </c>
       <c r="D40" t="str">
-        <v>06/12/2025</v>
+        <v>07/11/2025</v>
       </c>
       <c r="E40">
-        <v>182900</v>
+        <v>113280</v>
       </c>
       <c r="F40">
-        <v>155000</v>
+        <v>96000</v>
       </c>
       <c r="G40">
-        <v>27900</v>
+        <v>17280</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2109,25 +2109,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B41" t="str">
-        <v>Nova Instruments</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C41" t="str">
-        <v>S21/2025/032</v>
+        <v>S19/2025/031</v>
       </c>
       <c r="D41" t="str">
-        <v>10/12/2025</v>
+        <v>08/12/2025</v>
       </c>
       <c r="E41">
-        <v>199420</v>
+        <v>99120</v>
       </c>
       <c r="F41">
-        <v>169000</v>
+        <v>84000</v>
       </c>
       <c r="G41">
-        <v>30420</v>
+        <v>15120</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2026-01</v>
       </c>
       <c r="L41" t="str">
-        <v>08/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2156,25 +2156,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B42" t="str">
-        <v>Nova Instruments</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C42" t="str">
-        <v>S21/2025/033</v>
+        <v>S19/2025/032</v>
       </c>
       <c r="D42" t="str">
         <v>07/12/2025</v>
       </c>
       <c r="E42">
-        <v>194700</v>
+        <v>101480</v>
       </c>
       <c r="F42">
-        <v>165000</v>
+        <v>86000</v>
       </c>
       <c r="G42">
-        <v>29700</v>
+        <v>15480</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2203,31 +2203,31 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B43" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C43" t="str">
-        <v>S22/2025/031</v>
+        <v>S20/2025/031</v>
       </c>
       <c r="D43" t="str">
-        <v>20/12/2025</v>
+        <v>19/12/2025</v>
       </c>
       <c r="E43">
-        <v>218300</v>
+        <v>134520</v>
       </c>
       <c r="F43">
-        <v>185000</v>
+        <v>114000</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>16650</v>
+        <v>10260</v>
       </c>
       <c r="I43">
-        <v>16650</v>
+        <v>10260</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2026-01</v>
       </c>
       <c r="L43" t="str">
-        <v>12/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2250,25 +2250,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>24AAECC7789B1ZM</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B44" t="str">
-        <v>Coral Adhesives</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C44" t="str">
-        <v>S23/2025/031</v>
+        <v>S21/2025/031</v>
       </c>
       <c r="D44" t="str">
-        <v>18/12/2025</v>
+        <v>15/12/2025</v>
       </c>
       <c r="E44">
-        <v>200600</v>
+        <v>205320</v>
       </c>
       <c r="F44">
-        <v>170000</v>
+        <v>174000</v>
       </c>
       <c r="G44">
-        <v>30600</v>
+        <v>31320</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2026-01</v>
       </c>
       <c r="L44" t="str">
-        <v>09/01/2026</v>
+        <v>13/01/2026</v>
       </c>
       <c r="M44" t="str">
         <v>Yes</v>
@@ -2297,25 +2297,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B45" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C45" t="str">
-        <v>S24/2025/031</v>
+        <v>S21/2025/032</v>
       </c>
       <c r="D45" t="str">
-        <v>11/12/2025</v>
+        <v>14/12/2025</v>
       </c>
       <c r="E45">
-        <v>156940</v>
+        <v>210040</v>
       </c>
       <c r="F45">
-        <v>133000</v>
+        <v>178000</v>
       </c>
       <c r="G45">
-        <v>23940</v>
+        <v>32040</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>2026-01</v>
       </c>
       <c r="L45" t="str">
-        <v>08/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="M45" t="str">
         <v>Yes</v>
@@ -2344,25 +2344,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B46" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C46" t="str">
-        <v>S24/2025/032</v>
+        <v>S21/2025/033</v>
       </c>
       <c r="D46" t="str">
-        <v>12/12/2025</v>
+        <v>09/12/2025</v>
       </c>
       <c r="E46">
-        <v>164020</v>
+        <v>186440</v>
       </c>
       <c r="F46">
-        <v>139000</v>
+        <v>158000</v>
       </c>
       <c r="G46">
-        <v>25020</v>
+        <v>28440</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>2026-01</v>
       </c>
       <c r="L46" t="str">
-        <v>09/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="M46" t="str">
         <v>Yes</v>
@@ -2391,31 +2391,31 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B47" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C47" t="str">
-        <v>S24/2025/033</v>
+        <v>S22/2025/031</v>
       </c>
       <c r="D47" t="str">
-        <v>07/12/2025</v>
+        <v>05/12/2025</v>
       </c>
       <c r="E47">
-        <v>145140</v>
+        <v>201780</v>
       </c>
       <c r="F47">
-        <v>123000</v>
+        <v>171000</v>
       </c>
       <c r="G47">
-        <v>22140</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>15390</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>15390</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>2026-01</v>
       </c>
       <c r="L47" t="str">
-        <v>13/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="M47" t="str">
         <v>Yes</v>
@@ -2438,31 +2438,31 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>27AABCZ9934D1Z1</v>
+        <v>24AAECC7789B1ZM</v>
       </c>
       <c r="B48" t="str">
-        <v>Zenith Tooling</v>
+        <v>Coral Adhesives</v>
       </c>
       <c r="C48" t="str">
-        <v>S25/2025/031</v>
+        <v>S23/2025/031</v>
       </c>
       <c r="D48" t="str">
-        <v>08/12/2025</v>
+        <v>22/12/2025</v>
       </c>
       <c r="E48">
-        <v>37760</v>
+        <v>192340</v>
       </c>
       <c r="F48">
-        <v>32000</v>
+        <v>163000</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>29340</v>
       </c>
       <c r="H48">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2483,9 +2483,197 @@
         <v>N</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>09AAJFY5523C1Z3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Yamuna Agro Products</v>
+      </c>
+      <c r="C49" t="str">
+        <v>S24/2025/031</v>
+      </c>
+      <c r="D49" t="str">
+        <v>16/12/2025</v>
+      </c>
+      <c r="E49">
+        <v>145140</v>
+      </c>
+      <c r="F49">
+        <v>123000</v>
+      </c>
+      <c r="G49">
+        <v>22140</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="str">
+        <v>2026-01</v>
+      </c>
+      <c r="L49" t="str">
+        <v>10/01/2026</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>09AAJFY5523C1Z3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Yamuna Agro Products</v>
+      </c>
+      <c r="C50" t="str">
+        <v>S24/2025/032</v>
+      </c>
+      <c r="D50" t="str">
+        <v>20/12/2025</v>
+      </c>
+      <c r="E50">
+        <v>151040</v>
+      </c>
+      <c r="F50">
+        <v>128000</v>
+      </c>
+      <c r="G50">
+        <v>23040</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="str">
+        <v>2026-01</v>
+      </c>
+      <c r="L50" t="str">
+        <v>15/01/2026</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>09AAJFY5523C1Z3</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Yamuna Agro Products</v>
+      </c>
+      <c r="C51" t="str">
+        <v>S24/2025/033</v>
+      </c>
+      <c r="D51" t="str">
+        <v>14/12/2025</v>
+      </c>
+      <c r="E51">
+        <v>155760</v>
+      </c>
+      <c r="F51">
+        <v>132000</v>
+      </c>
+      <c r="G51">
+        <v>23760</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="str">
+        <v>2026-01</v>
+      </c>
+      <c r="L51" t="str">
+        <v>10/01/2026</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>27AABCZ9934D1Z1</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Zenith Tooling</v>
+      </c>
+      <c r="C52" t="str">
+        <v>S25/2025/031</v>
+      </c>
+      <c r="D52" t="str">
+        <v>09/12/2025</v>
+      </c>
+      <c r="E52">
+        <v>51920</v>
+      </c>
+      <c r="F52">
+        <v>44000</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>3960</v>
+      </c>
+      <c r="I52">
+        <v>3960</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="str">
+        <v>2026-01</v>
+      </c>
+      <c r="L52" t="str">
+        <v>12/01/2026</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v>N</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2568,13 +2756,13 @@
         <v>27/12/2025</v>
       </c>
       <c r="F5">
-        <v>31683</v>
+        <v>33099</v>
       </c>
       <c r="G5">
-        <v>26850</v>
+        <v>28050</v>
       </c>
       <c r="H5">
-        <v>4833</v>
+        <v>5049</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2589,7 +2777,7 @@
         <v>2026-01</v>
       </c>
       <c r="M5" t="str">
-        <v>14/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="N5" t="str">
         <v>Yes</v>
@@ -2615,13 +2803,13 @@
         <v>27/12/2025</v>
       </c>
       <c r="F6">
-        <v>30267</v>
+        <v>29736</v>
       </c>
       <c r="G6">
-        <v>25650</v>
+        <v>25200</v>
       </c>
       <c r="H6">
-        <v>4617</v>
+        <v>4536</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2636,7 +2824,7 @@
         <v>2026-01</v>
       </c>
       <c r="M6" t="str">
-        <v>17/01/2026</v>
+        <v>22/01/2026</v>
       </c>
       <c r="N6" t="str">
         <v>Yes</v>
